--- a/Sprint1/Doc/Change Log.xlsx
+++ b/Sprint1/Doc/Change Log.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sprintone\PaiNamNaeWebApp\Sprint1\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\ไปนำไปแหน่noti\PaiNamNaeWebApp\Sprint1\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCE92F8A-BE2E-4953-B3FD-358F17A1CA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B21CCFA-2269-4A6A-A4BA-EB6B891BD209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="61">
   <si>
     <t>New Estimates of Effort  Remaining at end of Day..</t>
   </si>
@@ -229,6 +229,9 @@
   <si>
     <t>ลบไฟล์ .env.example เพื่อความปลอดภัย และ Downgrade Prisma ลงมาเป็นเวอร์ชัน ^6.19.2</t>
   </si>
+  <si>
+    <t>เพิ่มหน้าview all notification</t>
+  </si>
 </sst>
 </file>
 
@@ -237,11 +240,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -442,59 +452,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -722,15 +733,15 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="11"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="24"/>
       <c r="L1" s="2" t="s">
         <v>1</v>
       </c>
@@ -802,7 +813,7 @@
       <c r="AA2" s="2"/>
     </row>
     <row r="3" spans="1:27" ht="114" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="19" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -855,7 +866,7 @@
       <c r="AA3" s="7"/>
     </row>
     <row r="4" spans="1:27" ht="114" customHeight="1">
-      <c r="A4" s="13"/>
+      <c r="A4" s="20"/>
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -906,7 +917,7 @@
       <c r="AA4" s="7"/>
     </row>
     <row r="5" spans="1:27" ht="114" customHeight="1">
-      <c r="A5" s="13"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
@@ -957,7 +968,7 @@
       <c r="AA5" s="7"/>
     </row>
     <row r="6" spans="1:27" ht="114" customHeight="1">
-      <c r="A6" s="13"/>
+      <c r="A6" s="20"/>
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
@@ -1008,7 +1019,7 @@
       <c r="AA6" s="7"/>
     </row>
     <row r="7" spans="1:27" ht="114" customHeight="1">
-      <c r="A7" s="13"/>
+      <c r="A7" s="20"/>
       <c r="B7" s="4" t="s">
         <v>14</v>
       </c>
@@ -1059,7 +1070,7 @@
       <c r="AA7" s="7"/>
     </row>
     <row r="8" spans="1:27" ht="114" customHeight="1">
-      <c r="A8" s="14"/>
+      <c r="A8" s="21"/>
       <c r="B8" s="5" t="s">
         <v>16</v>
       </c>
@@ -29895,7 +29906,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
@@ -29903,7 +29914,7 @@
     <col min="4" max="4" width="121.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="14.4">
       <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
@@ -29918,250 +29929,261 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.4">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.4">
-      <c r="A3" s="20"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.4">
-      <c r="A4" s="20"/>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.4">
-      <c r="A5" s="20"/>
-      <c r="B5" s="17" t="s">
+      <c r="A5" s="14"/>
+      <c r="B5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.4">
-      <c r="A6" s="20"/>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.4">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="14.4">
-      <c r="A8" s="20"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="14"/>
+      <c r="B8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.4">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="14.4">
-      <c r="A10" s="20"/>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="14"/>
+      <c r="B10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.4">
-      <c r="A11" s="20"/>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="14"/>
+      <c r="B11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.6">
-      <c r="A12" s="20"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="14"/>
+      <c r="B12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="16" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="14.4">
-      <c r="A13" s="20"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="14.4">
-      <c r="A14" s="20"/>
-      <c r="B14" s="17" t="s">
+      <c r="A14" s="14"/>
+      <c r="B14" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="14.4">
-      <c r="A15" s="20"/>
-      <c r="B15" s="17" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.4">
-      <c r="A16" s="20"/>
-      <c r="B16" s="18" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="14" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.4">
-      <c r="A17" s="20"/>
-      <c r="B17" s="18" t="s">
+      <c r="A17" s="14"/>
+      <c r="B17" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="14" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.4">
-      <c r="A18" s="20"/>
-      <c r="B18" s="18" t="s">
+      <c r="A18" s="14"/>
+      <c r="B18" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="14" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="18" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="14" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1">
       <c r="A21" s="10"/>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="14" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1">
+      <c r="B22" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Sprint1/Doc/Change Log.xlsx
+++ b/Sprint1/Doc/Change Log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pitim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25E43A07-D2B7-433D-AC50-61CED6C9E3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E73A72C-725A-4C14-AB2D-D1B322CAED9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Change log" sheetId="11" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="49">
   <si>
     <t>วันที่</t>
   </si>
@@ -158,6 +158,15 @@
   </si>
   <si>
     <t>แสดงข้อมูลติดต่อของผู้ขับและผู้โดยสาร</t>
+  </si>
+  <si>
+    <t>Add Robot Framework tests &amp; docs for Pickup Notification</t>
+  </si>
+  <si>
+    <t>Piti</t>
+  </si>
+  <si>
+    <t>testAPI โดยใช้AI Add Robot Framework tests &amp; docs for Pickup Notification</t>
   </si>
 </sst>
 </file>
@@ -165,9 +174,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d\ mmm\ yyyy"/>
+    <numFmt numFmtId="187" formatCode="d\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +236,13 @@
       <sz val="14"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Arial&quot;"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -255,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -272,7 +288,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -491,15 +509,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" customWidth="1"/>
-    <col min="4" max="4" width="121.42578125" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="121.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="14.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -513,7 +531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="14.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -527,7 +545,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="14.4">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -538,7 +556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="14.4">
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
@@ -549,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" ht="14.4">
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
@@ -560,7 +578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" ht="14.4">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -571,7 +589,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" ht="14.4">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -585,7 +603,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" ht="14.4">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>11</v>
@@ -597,7 +615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" ht="14.4">
       <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
@@ -611,7 +629,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" ht="14.4">
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
@@ -622,7 +640,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" ht="14.4">
       <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
@@ -633,7 +651,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="15.6">
       <c r="A12" s="1"/>
       <c r="B12" s="5" t="s">
         <v>11</v>
@@ -645,7 +663,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" ht="14.4">
       <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
@@ -656,7 +674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" ht="14.4">
       <c r="B14" s="1" t="s">
         <v>26</v>
       </c>
@@ -667,7 +685,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" ht="14.4">
       <c r="B15" s="1" t="s">
         <v>28</v>
       </c>
@@ -678,7 +696,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" ht="14.4">
       <c r="B16" s="8" t="s">
         <v>30</v>
       </c>
@@ -689,7 +707,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" ht="14.4">
       <c r="B17" s="8" t="s">
         <v>32</v>
       </c>
@@ -700,7 +718,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" ht="14.4">
       <c r="B18" s="8" t="s">
         <v>34</v>
       </c>
@@ -748,7 +766,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" ht="14.4">
       <c r="B22" s="1" t="s">
         <v>5</v>
       </c>
@@ -759,7 +777,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" ht="14.4">
       <c r="B23" s="1" t="s">
         <v>14</v>
       </c>
@@ -770,7 +788,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" ht="14.4">
       <c r="B24" s="1" t="s">
         <v>44</v>
       </c>
@@ -779,6 +797,20 @@
       </c>
       <c r="D24" s="1" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1">
+      <c r="A25" s="13">
+        <v>46072</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
